--- a/StructureDefinition-Laboratorieanalysresultat-Observerat-halsotillstand.xlsx
+++ b/StructureDefinition-Laboratorieanalysresultat-Observerat-halsotillstand.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Laboratorieanalysresultat-Observerat-halsotillstand.xlsx
+++ b/StructureDefinition-Laboratorieanalysresultat-Observerat-halsotillstand.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Laboratorieanalysresultat : Observerat hälsotillstånd).</t>
+    <t>Resultat av en laboratorieanalys. 
+Ett laboratorieanalysresultat kan utgöras av t.ex. ett fynd (som har sina egenskaper) eller ett mätvärde.  
+Exempel på fynd är en viss bakterieart eller en viss typ av virus.   
+Exempel på ett fynds egenskaper är serotyp, subserotyp och koncentration.</t>
   </si>
   <si>
     <t>Purpose</t>
